--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-allergie-intolerance.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-allergie-intolerance.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AllergyIntolerance - Fr AllergyIntolerance</t>
+    <t>AllergyIntolerance - Fr Allergie et intolérance</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -539,7 +539,7 @@
     <t>The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-value-set-condition-verification-status</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-value-set-allergie-intolerance-verification-status</t>
   </si>
   <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
@@ -684,11 +684,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
 </t>
   </si>
   <si>
-    <t>Who the sensitivity is for</t>
+    <t>Patient concerné par l'allergie ou intolérance</t>
   </si>
   <si>
     <t>The patient who has the allergy or intolerance.</t>
@@ -729,7 +729,7 @@
 AgePeriodRangestring</t>
   </si>
   <si>
-    <t>When allergy or intolerance was identified</t>
+    <t>Date d'identification d'allergie ou d'intolérance</t>
   </si>
   <si>
     <t>Estimated or actual date,  date-time, or age when allergy or intolerance was identified.</t>
@@ -1462,7 +1462,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="50.3046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="152.35546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1477,7 +1477,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.16796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="86.171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3404,7 +3404,7 @@
         <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>79</v>
@@ -3622,7 +3622,7 @@
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>79</v>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-allergie-intolerance.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-allergie-intolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
